--- a/docs/excel_files/Ricks Music progress.xlsx
+++ b/docs/excel_files/Ricks Music progress.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\docs\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCB74E51-4962-4449-8AAA-938E45D4B663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76188BA-3A32-4284-B1B7-F403FF8A8BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
+    <workbookView xWindow="23016" yWindow="12768" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Exceptions &amp; Logging" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="89">
   <si>
     <t>module.py</t>
   </si>
@@ -291,9 +291,6 @@
     <t>extracted album art</t>
   </si>
   <si>
-    <t>set album art</t>
-  </si>
-  <si>
     <t>54-40</t>
   </si>
   <si>
@@ -348,13 +345,73 @@
     <t>has embedded art</t>
   </si>
   <si>
-    <t>Avenged Seven Fold</t>
-  </si>
-  <si>
     <t>Cream</t>
   </si>
   <si>
     <t>Jack Bruce</t>
+  </si>
+  <si>
+    <t>Bachman-Turner Overdrive</t>
+  </si>
+  <si>
+    <t>Huey Lewis &amp; The News</t>
+  </si>
+  <si>
+    <t>Bad Company</t>
+  </si>
+  <si>
+    <t>Barenaked Ladies</t>
+  </si>
+  <si>
+    <t>Beach Boys</t>
+  </si>
+  <si>
+    <t>Bee Gees</t>
+  </si>
+  <si>
+    <t>Stephen Page</t>
+  </si>
+  <si>
+    <t>Avenged Sevenfold</t>
+  </si>
+  <si>
+    <t>Beth Hart and Joe Bonamassa</t>
+  </si>
+  <si>
+    <t>Blondie</t>
+  </si>
+  <si>
+    <t>Blu Cantrell</t>
+  </si>
+  <si>
+    <t>Blue Rodeo</t>
+  </si>
+  <si>
+    <t>Bonnie Raitt</t>
+  </si>
+  <si>
+    <t>Album Directories Normalized</t>
+  </si>
+  <si>
+    <t>Bonnie Tyler</t>
+  </si>
+  <si>
+    <t>Boston</t>
+  </si>
+  <si>
+    <t>set comp album art</t>
+  </si>
+  <si>
+    <t>Brad Paisley</t>
+  </si>
+  <si>
+    <t>Brandi Carlile</t>
+  </si>
+  <si>
+    <t>Bruce Springsteen</t>
+  </si>
+  <si>
+    <t>Bryan Adams</t>
   </si>
 </sst>
 </file>
@@ -438,7 +495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -455,12 +512,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1106,690 +1195,1986 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1790D277-535D-4916-A268-6363928B98F0}">
-  <dimension ref="B2:N18"/>
+  <dimension ref="B1:O64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.42578125" customWidth="1"/>
-    <col min="14" max="14" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="8"/>
+    <col min="2" max="2" width="27.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.28515625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" style="8" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" style="8" customWidth="1"/>
+    <col min="12" max="12" width="10" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" style="8" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="8" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="2:15" s="11" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="B1" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F1" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="I1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B24" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B30" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B31" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B32" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="C32" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B33" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="9"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+      <c r="O46" s="9"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="9"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+      <c r="O48" s="9"/>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9"/>
+      <c r="O49" s="9"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="9"/>
+      <c r="O50" s="9"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+      <c r="O51" s="9"/>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="9"/>
+      <c r="O52" s="9"/>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9"/>
+      <c r="O53" s="9"/>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+      <c r="M54" s="9"/>
+      <c r="N54" s="9"/>
+      <c r="O54" s="9"/>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
+      <c r="N55" s="9"/>
+      <c r="O55" s="9"/>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="9"/>
+      <c r="L56" s="9"/>
+      <c r="M56" s="9"/>
+      <c r="N56" s="9"/>
+      <c r="O56" s="9"/>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+      <c r="M57" s="9"/>
+      <c r="N57" s="9"/>
+      <c r="O57" s="9"/>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9"/>
+      <c r="O59" s="9"/>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="9"/>
+      <c r="M60" s="9"/>
+      <c r="N60" s="9"/>
+      <c r="O60" s="9"/>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
+      <c r="M61" s="9"/>
+      <c r="N61" s="9"/>
+      <c r="O61" s="9"/>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+      <c r="M62" s="9"/>
+      <c r="N62" s="9"/>
+      <c r="O62" s="9"/>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="9"/>
+      <c r="M63" s="9"/>
+      <c r="N63" s="9"/>
+      <c r="O63" s="9"/>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
+      <c r="M64" s="9"/>
+      <c r="N64" s="9"/>
+      <c r="O64" s="9"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:XFD64">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/excel_files/Ricks Music progress.xlsx
+++ b/docs/excel_files/Ricks Music progress.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\docs\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705ECA20-F889-4920-89C7-1CF6915FB750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EB7741-0B0D-4FA1-8BDC-93D6557D708A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23016" yWindow="12768" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
+    <workbookView xWindow="23016" yWindow="12768" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="#" sheetId="4" r:id="rId1"/>
     <sheet name="A" sheetId="3" r:id="rId2"/>
     <sheet name="B" sheetId="5" r:id="rId3"/>
     <sheet name="C" sheetId="6" r:id="rId4"/>
-    <sheet name="H" sheetId="11" r:id="rId5"/>
-    <sheet name="J" sheetId="13" r:id="rId6"/>
-    <sheet name="R" sheetId="15" r:id="rId7"/>
-    <sheet name="S" sheetId="14" r:id="rId8"/>
-    <sheet name="template" sheetId="16" r:id="rId9"/>
+    <sheet name="D" sheetId="17" r:id="rId5"/>
+    <sheet name="H" sheetId="11" r:id="rId6"/>
+    <sheet name="J" sheetId="13" r:id="rId7"/>
+    <sheet name="R" sheetId="15" r:id="rId8"/>
+    <sheet name="S" sheetId="14" r:id="rId9"/>
+    <sheet name="T" sheetId="18" r:id="rId10"/>
+    <sheet name="template" sheetId="16" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="71">
   <si>
     <t>NA</t>
   </si>
@@ -230,10 +232,31 @@
     <t>artist 1</t>
   </si>
   <si>
-    <t>genre updated</t>
+    <t>metadata updated</t>
   </si>
   <si>
-    <t>gnere updated</t>
+    <t>metdata updated</t>
+  </si>
+  <si>
+    <t>in transfer dir</t>
+  </si>
+  <si>
+    <t>Daryll Hall</t>
+  </si>
+  <si>
+    <t>Dave Matthews Band</t>
+  </si>
+  <si>
+    <t>David Bowie</t>
+  </si>
+  <si>
+    <t>Tin Machine</t>
+  </si>
+  <si>
+    <t>David Lindley</t>
+  </si>
+  <si>
+    <t>David Wilcox</t>
   </si>
 </sst>
 </file>
@@ -303,7 +326,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="57">
     <dxf>
       <font>
         <b val="0"/>
@@ -450,6 +473,18 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
       </font>
@@ -471,6 +506,186 @@
           <bgColor theme="3" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -878,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832F30EA-A032-48C6-ABA2-2D477863AE50}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -895,7 +1110,7 @@
     <col min="14" max="14" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -939,10 +1154,13 @@
         <v>62</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -986,10 +1204,13 @@
         <v>3</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1033,18 +1254,32 @@
         <v>3</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD3">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="3">
+    <cfRule type="expression" dxfId="54" priority="6">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O3">
+    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1052,561 +1287,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5498BB1C-2009-4B75-8E63-FA8EC8D63D36}">
-  <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A2:XFD11">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
-      <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
-      <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="3">
-      <formula>MOD(ROW(), 2) = 0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B08846-0C86-4F4B-BBEE-7D9E018F9FC5}">
-  <dimension ref="A1:O48"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773E741D-F1A5-41A0-B656-3E8F5BB0844F}">
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -1625,7 +1308,7 @@
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1666,15 +1349,18 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -1716,12 +1402,15 @@
         <v>3</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -1763,668 +1452,265 @@
         <v>3</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2440,8 +1726,9 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2457,8 +1744,9 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2474,8 +1762,9 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2491,8 +1780,9 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2508,8 +1798,9 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2525,8 +1816,9 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2542,8 +1834,9 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2559,8 +1852,9 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2576,8 +1870,9 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2593,8 +1888,9 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2610,8 +1906,9 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2627,8 +1924,9 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2644,8 +1942,9 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2661,8 +1960,9 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2678,8 +1978,9 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2695,8 +1996,9 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2712,265 +2014,52 @@
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
+      <c r="P34" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:N48 P2:XFD48 N18:O48">
-    <cfRule type="cellIs" dxfId="26" priority="4" operator="equal">
+  <conditionalFormatting sqref="A4:XFD34 A3:L3 P3:XFD3">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="6">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:P2">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="3">
+    <cfRule type="expression" dxfId="9" priority="6">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:XFD2">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:XFD2">
+    <cfRule type="expression" dxfId="6" priority="9">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:O3">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2978,1027 +2067,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{241DFEF1-9AEF-4655-A27C-D75DC9300F5B}">
-  <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.28515625" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A2:N2 P2:XFD2 A3:XFD34 L2:L8">
-    <cfRule type="expression" dxfId="20" priority="12">
-      <formula>MOD(ROW(), 2) = 0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:XFD34 A2:N2 P2:XFD2 L2:L8">
-    <cfRule type="cellIs" dxfId="19" priority="10" operator="equal">
-      <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
-      <formula>"Yes"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O13">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
-      <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
-      <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="3">
-      <formula>MOD(ROW(), 2) = 0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC1F7B8-E9E3-4996-94BF-2F4D98772BE4}">
-  <dimension ref="A1:O33"/>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE04A26-E0D7-4F6E-9369-31B8371FBE59}">
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -4017,7 +2088,7 @@
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -4061,57 +2132,63 @@
         <v>62</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -4127,8 +2204,9 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -4144,8 +2222,9 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -4161,8 +2240,9 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -4178,8 +2258,9 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -4195,8 +2276,9 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -4212,8 +2294,9 @@
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -4229,8 +2312,9 @@
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -4246,8 +2330,9 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -4263,8 +2348,9 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -4280,8 +2366,9 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -4297,8 +2384,9 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -4314,8 +2402,9 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -4331,8 +2420,9 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -4348,8 +2438,9 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4365,8 +2456,9 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4382,8 +2474,9 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4399,8 +2492,9 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -4416,8 +2510,9 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4433,8 +2528,9 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -4450,8 +2546,9 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -4467,8 +2564,9 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -4484,8 +2582,9 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -4501,8 +2600,9 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -4518,8 +2618,9 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -4535,8 +2636,9 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -4552,8 +2654,9 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -4569,8 +2672,9 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -4586,8 +2690,9 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -4603,8 +2708,9 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -4620,8 +2726,9 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -4637,16 +2744,17 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4654,9 +2762,3100 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B60845-B986-4971-AC1C-D231CB8E9BF9}">
-  <dimension ref="A1:O33"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5498BB1C-2009-4B75-8E63-FA8EC8D63D36}">
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:XFD11">
+    <cfRule type="cellIs" dxfId="50" priority="7" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="8" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="9">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O11">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="3">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="4" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="5" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="6">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B08846-0C86-4F4B-BBEE-7D9E018F9FC5}">
+  <dimension ref="A1:P48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:O48 Q2:XFD48 N18:P48">
+    <cfRule type="cellIs" dxfId="41" priority="4" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="5" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="6">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P17">
+    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="3">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{241DFEF1-9AEF-4655-A27C-D75DC9300F5B}">
+  <dimension ref="A1:P33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:P12">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="3">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:XFD2 A13:XFD33 P3:XFD12">
+    <cfRule type="cellIs" dxfId="32" priority="10" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="11" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:XFD2 A13:XFD33 P3:XFD12">
+    <cfRule type="expression" dxfId="30" priority="12">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A665A9A6-A955-425D-A292-ED453B420318}">
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -4675,7 +5874,7 @@
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -4719,12 +5918,15 @@
         <v>62</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -4766,78 +5968,213 @@
         <v>3</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -4853,8 +6190,9 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -4870,8 +6208,9 @@
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -4887,8 +6226,9 @@
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -4904,8 +6244,9 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -4921,8 +6262,9 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -4938,8 +6280,9 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -4955,8 +6298,9 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -4972,8 +6316,9 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -4989,8 +6334,9 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -5006,8 +6352,9 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -5023,8 +6370,9 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -5040,8 +6388,9 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -5057,8 +6406,9 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -5074,8 +6424,9 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -5091,8 +6442,9 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -5108,8 +6460,9 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -5125,8 +6478,9 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -5142,8 +6496,9 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -5159,8 +6514,9 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -5176,8 +6532,9 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -5193,8 +6550,9 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -5210,8 +6568,9 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -5227,8 +6586,9 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -5244,8 +6604,9 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -5261,8 +6622,9 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -5278,8 +6640,9 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -5295,16 +6658,17 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="27" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5312,9 +6676,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E4E354-CC46-4D69-85EF-A6DDA23BD060}">
-  <dimension ref="A1:O33"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC1F7B8-E9E3-4996-94BF-2F4D98772BE4}">
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -5331,9 +6695,10 @@
     <col min="12" max="12" width="10.28515625" customWidth="1"/>
     <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -5377,12 +6742,15 @@
         <v>62</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -5421,13 +6789,16 @@
         <v>3</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -5443,8 +6814,9 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -5460,8 +6832,9 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -5477,8 +6850,9 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -5494,8 +6868,9 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -5511,8 +6886,9 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -5528,8 +6904,9 @@
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -5545,8 +6922,9 @@
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -5562,8 +6940,9 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -5579,8 +6958,9 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -5596,8 +6976,9 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -5613,8 +6994,9 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -5630,8 +7012,9 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -5647,8 +7030,9 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -5664,8 +7048,9 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -5681,8 +7066,9 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -5698,8 +7084,9 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -5715,8 +7102,9 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -5732,8 +7120,9 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -5749,8 +7138,9 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -5766,8 +7156,9 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -5783,8 +7174,9 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -5800,8 +7192,9 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -5817,8 +7210,9 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -5834,8 +7228,9 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -5851,8 +7246,9 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -5868,8 +7264,9 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -5885,8 +7282,9 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -5902,8 +7300,9 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -5919,8 +7318,9 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -5936,8 +7336,9 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -5953,16 +7354,17 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="24" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5970,9 +7372,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C91933-1FED-40CE-A7F7-694A14E79AF4}">
-  <dimension ref="A1:O33"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B60845-B986-4971-AC1C-D231CB8E9BF9}">
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -5989,9 +7391,10 @@
     <col min="12" max="12" width="10.28515625" customWidth="1"/>
     <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -6035,12 +7438,15 @@
         <v>62</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -6082,10 +7488,13 @@
         <v>3</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -6101,8 +7510,9 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -6118,8 +7528,9 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -6135,8 +7546,9 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -6152,8 +7564,9 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -6169,8 +7582,9 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -6186,8 +7600,9 @@
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -6203,8 +7618,9 @@
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -6220,8 +7636,9 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -6237,8 +7654,9 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -6254,8 +7672,9 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -6271,8 +7690,9 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -6288,8 +7708,9 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -6305,8 +7726,9 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -6322,8 +7744,9 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -6339,8 +7762,9 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -6356,8 +7780,9 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -6373,8 +7798,9 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -6390,8 +7816,9 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -6407,8 +7834,9 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -6424,8 +7852,9 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -6441,8 +7870,9 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -6458,8 +7888,9 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -6475,8 +7906,9 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -6492,8 +7924,9 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -6509,8 +7942,9 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -6526,8 +7960,9 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -6543,8 +7978,9 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -6560,8 +7996,9 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -6577,8 +8014,9 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -6594,8 +8032,9 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -6611,16 +8050,17 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="21" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6628,9 +8068,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE04A26-E0D7-4F6E-9369-31B8371FBE59}">
-  <dimension ref="A1:O33"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E4E354-CC46-4D69-85EF-A6DDA23BD060}">
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -6647,9 +8087,10 @@
     <col min="12" max="12" width="10.28515625" customWidth="1"/>
     <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -6690,60 +8131,66 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -6759,8 +8206,9 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -6776,8 +8224,9 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -6793,8 +8242,9 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -6810,8 +8260,9 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -6827,8 +8278,9 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -6844,8 +8296,9 @@
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -6861,8 +8314,9 @@
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -6878,8 +8332,9 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -6895,8 +8350,9 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -6912,8 +8368,9 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -6929,8 +8386,9 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -6946,8 +8404,9 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -6963,8 +8422,9 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -6980,8 +8440,9 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -6997,8 +8458,9 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -7014,8 +8476,9 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -7031,8 +8494,9 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -7048,8 +8512,9 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -7065,8 +8530,9 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -7082,8 +8548,9 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -7099,8 +8566,9 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -7116,8 +8584,9 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -7133,8 +8602,9 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -7150,8 +8620,9 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -7167,8 +8638,9 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -7184,8 +8656,9 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -7201,8 +8674,9 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -7218,8 +8692,9 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -7235,8 +8710,9 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -7252,8 +8728,9 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -7269,16 +8746,713 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C91933-1FED-40CE-A7F7-694A14E79AF4}">
+  <dimension ref="A1:P33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:XFD33">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/excel_files/Ricks Music progress.xlsx
+++ b/docs/excel_files/Ricks Music progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\docs\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EB7741-0B0D-4FA1-8BDC-93D6557D708A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE84A0F8-F95E-4C0C-B393-AD57A92A32D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23016" yWindow="12768" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
+    <workbookView xWindow="23016" yWindow="12768" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="#" sheetId="4" r:id="rId1"/>
@@ -18,12 +18,14 @@
     <sheet name="B" sheetId="5" r:id="rId3"/>
     <sheet name="C" sheetId="6" r:id="rId4"/>
     <sheet name="D" sheetId="17" r:id="rId5"/>
-    <sheet name="H" sheetId="11" r:id="rId6"/>
-    <sheet name="J" sheetId="13" r:id="rId7"/>
-    <sheet name="R" sheetId="15" r:id="rId8"/>
-    <sheet name="S" sheetId="14" r:id="rId9"/>
-    <sheet name="T" sheetId="18" r:id="rId10"/>
-    <sheet name="template" sheetId="16" r:id="rId11"/>
+    <sheet name="E" sheetId="19" r:id="rId6"/>
+    <sheet name="H" sheetId="11" r:id="rId7"/>
+    <sheet name="J" sheetId="13" r:id="rId8"/>
+    <sheet name="O" sheetId="20" r:id="rId9"/>
+    <sheet name="R" sheetId="15" r:id="rId10"/>
+    <sheet name="S" sheetId="14" r:id="rId11"/>
+    <sheet name="T" sheetId="18" r:id="rId12"/>
+    <sheet name="template" sheetId="16" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="86">
   <si>
     <t>NA</t>
   </si>
@@ -258,6 +260,51 @@
   <si>
     <t>David Wilcox</t>
   </si>
+  <si>
+    <t>Dire Straits</t>
+  </si>
+  <si>
+    <t>Dixie Chicks</t>
+  </si>
+  <si>
+    <t>Dolly Parton</t>
+  </si>
+  <si>
+    <t>Dwight Yoakam</t>
+  </si>
+  <si>
+    <t>Double Trouble</t>
+  </si>
+  <si>
+    <t>Duffy</t>
+  </si>
+  <si>
+    <t>Ed Sheeran</t>
+  </si>
+  <si>
+    <t>Electric Light Orchestra</t>
+  </si>
+  <si>
+    <t>Elle King</t>
+  </si>
+  <si>
+    <t>Elton John</t>
+  </si>
+  <si>
+    <t>Elvis Presley</t>
+  </si>
+  <si>
+    <t>Eric Clapton</t>
+  </si>
+  <si>
+    <t>Eva Cassidy</t>
+  </si>
+  <si>
+    <t>Olivia Newton John</t>
+  </si>
+  <si>
+    <t>at a single man</t>
+  </si>
 </sst>
 </file>
 
@@ -326,7 +373,55 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="57">
+  <dxfs count="63">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1262,24 +1357,24 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD3">
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="5" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="6">
+    <cfRule type="expression" dxfId="60" priority="6">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O3">
-    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="3">
+    <cfRule type="expression" dxfId="57" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1288,6 +1383,1398 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E4E354-CC46-4D69-85EF-A6DDA23BD060}">
+  <dimension ref="A1:P33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:XFD33">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="3">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C91933-1FED-40CE-A7F7-694A14E79AF4}">
+  <dimension ref="A1:P33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:XFD33">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="3">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773E741D-F1A5-41A0-B656-3E8F5BB0844F}">
   <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2017,7 +3504,29 @@
       <c r="P34" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A4:XFD34 A3:L3 P3:XFD3">
+  <conditionalFormatting sqref="A3:O3">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="3">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:P2">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="6">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:XFD34">
     <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -2028,38 +3537,14 @@
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:P2">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+  <conditionalFormatting sqref="P2:XFD3">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="6">
-      <formula>MOD(ROW(), 2) = 0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:XFD2">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
-      <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
-      <formula>"Yes"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:XFD2">
-    <cfRule type="expression" dxfId="6" priority="9">
-      <formula>MOD(ROW(), 2) = 0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3:O3">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
-      <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
-      <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2067,7 +3552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE04A26-E0D7-4F6E-9369-31B8371FBE59}">
   <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2748,13 +4233,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3333,33 +4818,33 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD11">
-    <cfRule type="cellIs" dxfId="50" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="7" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="8" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="9">
+    <cfRule type="expression" dxfId="54" priority="9">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O11">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="3">
+    <cfRule type="expression" dxfId="51" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="5" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="6">
+    <cfRule type="expression" dxfId="48" priority="6">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4799,24 +6284,24 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:O48 Q2:XFD48 N18:P48">
-    <cfRule type="cellIs" dxfId="41" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="5" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="6">
+    <cfRule type="expression" dxfId="45" priority="6">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P17">
-    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="3">
+    <cfRule type="expression" dxfId="42" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5826,6 +7311,998 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:P12">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="3">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3:XFD12 Q2:XFD2 A13:XFD33">
+    <cfRule type="cellIs" dxfId="38" priority="10" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="11" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:XFD2 P3:XFD12 A13:XFD33">
+    <cfRule type="expression" dxfId="36" priority="12">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A665A9A6-A955-425D-A292-ED453B420318}">
+  <dimension ref="A1:P31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:XFD31">
     <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -5836,25 +8313,12 @@
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:XFD2 A13:XFD33 P3:XFD12">
-    <cfRule type="cellIs" dxfId="32" priority="10" operator="equal">
-      <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="11" operator="equal">
-      <formula>"Yes"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:XFD2 A13:XFD33 P3:XFD12">
-    <cfRule type="expression" dxfId="30" priority="12">
-      <formula>MOD(ROW(), 2) = 0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A665A9A6-A955-425D-A292-ED453B420318}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16921A6F-7CB8-4ECC-B4F3-AFD04063C385}">
   <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5926,7 +8390,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -5976,7 +8440,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -6009,7 +8473,7 @@
         <v>3</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>3</v>
@@ -6018,15 +8482,15 @@
         <v>3</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -6068,114 +8532,60 @@
         <v>3</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -6193,7 +8603,9 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -6662,13 +9074,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6676,7 +9088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC1F7B8-E9E3-4996-94BF-2F4D98772BE4}">
   <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7358,13 +9770,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="3">
+    <cfRule type="expression" dxfId="30" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7372,7 +9784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B60845-B986-4971-AC1C-D231CB8E9BF9}">
   <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8054,13 +10466,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="3">
+    <cfRule type="expression" dxfId="27" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8068,8 +10480,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E4E354-CC46-4D69-85EF-A6DDA23BD060}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2183BA-4B28-4F00-8FAE-962779201001}">
   <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8087,7 +10499,6 @@
     <col min="12" max="12" width="10.28515625" customWidth="1"/>
     <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -8131,7 +10542,7 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>64</v>
@@ -8142,7 +10553,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -8187,7 +10598,7 @@
         <v>3</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -8750,709 +11161,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="3">
-      <formula>MOD(ROW(), 2) = 0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C91933-1FED-40CE-A7F7-694A14E79AF4}">
-  <dimension ref="A1:P33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.28515625" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
-      <formula>"No"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
-      <formula>"Yes"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/excel_files/Ricks Music progress.xlsx
+++ b/docs/excel_files/Ricks Music progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\docs\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE84A0F8-F95E-4C0C-B393-AD57A92A32D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07D467E-A059-4EFD-A76D-1D3932C95F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23016" yWindow="12768" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="86">
   <si>
     <t>NA</t>
   </si>
@@ -303,7 +303,7 @@
     <t>Olivia Newton John</t>
   </si>
   <si>
-    <t>at a single man</t>
+    <t>Elton John &amp; Leon Russell</t>
   </si>
 </sst>
 </file>
@@ -2064,13 +2064,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2760,13 +2760,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="3">
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3505,46 +3505,46 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:O3">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="3">
+    <cfRule type="expression" dxfId="12" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:P2">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="6">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:XFD34">
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="11" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="6" priority="12">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:XFD3">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="3" priority="9">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4233,13 +4233,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8319,7 +8319,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16921A6F-7CB8-4ECC-B4F3-AFD04063C385}">
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -8473,7 +8473,7 @@
         <v>3</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>3</v>
@@ -8482,7 +8482,7 @@
         <v>3</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>13</v>
@@ -8532,7 +8532,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>13</v>
@@ -8543,87 +8543,205 @@
         <v>80</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
+        <v>85</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
+        <v>81</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -9072,15 +9190,33 @@
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
     </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:XFD34">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="30" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9770,13 +9906,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="3">
+    <cfRule type="expression" dxfId="27" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10466,13 +10602,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="3">
+    <cfRule type="expression" dxfId="24" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11161,13 +11297,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="21" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/excel_files/Ricks Music progress.xlsx
+++ b/docs/excel_files/Ricks Music progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\docs\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07D467E-A059-4EFD-A76D-1D3932C95F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DC19FF-044D-4A4F-B65D-F6F7B30702FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23016" yWindow="12768" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
+    <workbookView xWindow="23016" yWindow="12768" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="#" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="87">
   <si>
     <t>NA</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>Barenaked Ladies</t>
-  </si>
-  <si>
-    <t>Beach Boys</t>
   </si>
   <si>
     <t>Bee Gees</t>
@@ -305,6 +302,12 @@
   <si>
     <t>Elton John &amp; Leon Russell</t>
   </si>
+  <si>
+    <t>The Beach Boys</t>
+  </si>
+  <si>
+    <t>Derek And The Dominos</t>
+  </si>
 </sst>
 </file>
 
@@ -373,7 +376,31 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="66">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1213,7 +1240,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -1234,7 +1261,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -1246,13 +1273,13 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -1357,24 +1384,24 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD3">
-    <cfRule type="cellIs" dxfId="62" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="5" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="6">
+    <cfRule type="expression" dxfId="63" priority="6">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O3">
-    <cfRule type="cellIs" dxfId="59" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="3">
+    <cfRule type="expression" dxfId="60" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1412,7 +1439,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -1433,7 +1460,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -1445,18 +1472,18 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -2064,13 +2091,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="3">
+    <cfRule type="expression" dxfId="21" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2108,7 +2135,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -2129,7 +2156,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -2141,18 +2168,18 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -2760,13 +2787,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2776,7 +2803,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773E741D-F1A5-41A0-B656-3E8F5BB0844F}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -2803,7 +2830,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -2824,7 +2851,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -2836,18 +2863,18 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -2892,12 +2919,12 @@
         <v>3</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -2946,22 +2973,54 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -3503,48 +3562,77 @@
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
     </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:O3">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+  <conditionalFormatting sqref="A4:O4">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="3">
+    <cfRule type="expression" dxfId="15" priority="9">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:P2">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+  <conditionalFormatting sqref="A3:P3">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="6">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:XFD34">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+  <conditionalFormatting sqref="A2:XFD2">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="12">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:XFD3">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+  <conditionalFormatting sqref="A5:XFD35">
+    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="17" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="9">
+    <cfRule type="expression" dxfId="6" priority="18">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3:XFD4">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="14" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="15">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3581,7 +3669,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -3602,7 +3690,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -3614,18 +3702,18 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -4274,7 +4362,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -4295,7 +4383,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -4307,13 +4395,13 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -4768,7 +4856,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>3</v>
@@ -4818,33 +4906,33 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD11">
-    <cfRule type="cellIs" dxfId="56" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="7" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="8" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="9">
+    <cfRule type="expression" dxfId="57" priority="9">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O11">
-    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="3">
+    <cfRule type="expression" dxfId="54" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="5" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="6">
+    <cfRule type="expression" dxfId="51" priority="6">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4854,7 +4942,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B08846-0C86-4F4B-BBEE-7D9E018F9FC5}">
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -4882,7 +4970,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -4903,7 +4991,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -4915,13 +5003,13 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -5126,7 +5214,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>3</v>
@@ -5171,7 +5259,7 @@
         <v>3</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -5221,7 +5309,7 @@
         <v>3</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -5371,12 +5459,12 @@
         <v>3</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>3</v>
@@ -5421,7 +5509,7 @@
         <v>3</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -5476,7 +5564,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>3</v>
@@ -5521,7 +5609,7 @@
         <v>3</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -5621,7 +5709,7 @@
         <v>3</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -5675,54 +5763,22 @@
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -6264,44 +6320,26 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:O48 Q2:XFD48 N18:P48">
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="equal">
+  <conditionalFormatting sqref="A2:O47 Q2:XFD47 N17:P47">
+    <cfRule type="cellIs" dxfId="50" priority="4" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="5" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="6">
+    <cfRule type="expression" dxfId="48" priority="6">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
-    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
+  <conditionalFormatting sqref="P2:P16">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="3">
+    <cfRule type="expression" dxfId="45" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6339,7 +6377,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -6360,7 +6398,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -6372,18 +6410,18 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -6433,7 +6471,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -6483,7 +6521,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -6533,7 +6571,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
@@ -6583,7 +6621,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>3</v>
@@ -6633,7 +6671,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
@@ -6683,7 +6721,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>3</v>
@@ -6733,7 +6771,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>3</v>
@@ -6833,7 +6871,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>3</v>
@@ -6883,7 +6921,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>3</v>
@@ -7311,26 +7349,26 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:P12">
-    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="3">
+    <cfRule type="expression" dxfId="42" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:XFD12 Q2:XFD2 A13:XFD33">
-    <cfRule type="cellIs" dxfId="38" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="10" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="11" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:XFD2 P3:XFD12 A13:XFD33">
-    <cfRule type="expression" dxfId="36" priority="12">
+    <cfRule type="expression" dxfId="39" priority="12">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7340,7 +7378,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A665A9A6-A955-425D-A292-ED453B420318}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -7367,7 +7405,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -7388,7 +7426,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -7400,18 +7438,18 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -7461,7 +7499,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -7511,7 +7549,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -7561,7 +7599,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
@@ -7611,7 +7649,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>3</v>
@@ -7661,7 +7699,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
@@ -7706,12 +7744,12 @@
         <v>3</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>3</v>
@@ -7761,7 +7799,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>3</v>
@@ -7811,7 +7849,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>3</v>
@@ -7856,12 +7894,12 @@
         <v>3</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>3</v>
@@ -7911,7 +7949,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>3</v>
@@ -7956,26 +7994,58 @@
         <v>3</v>
       </c>
       <c r="P12" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
@@ -8301,15 +8371,33 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
     </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:XFD31">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:XFD32">
+    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="3">
+    <cfRule type="expression" dxfId="36" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8346,7 +8434,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -8367,7 +8455,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -8379,18 +8467,18 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -8440,7 +8528,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -8490,7 +8578,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -8540,7 +8628,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
@@ -8590,7 +8678,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>3</v>
@@ -8640,7 +8728,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
@@ -8690,7 +8778,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>3</v>
@@ -8740,7 +8828,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -9210,13 +9298,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD34">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="3">
+    <cfRule type="expression" dxfId="33" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9254,7 +9342,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -9275,7 +9363,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -9287,13 +9375,13 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -9906,13 +9994,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="3">
+    <cfRule type="expression" dxfId="30" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9950,7 +10038,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -9971,7 +10059,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -9983,13 +10071,13 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -10602,13 +10690,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="3">
+    <cfRule type="expression" dxfId="27" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10645,7 +10733,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
@@ -10666,7 +10754,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -10678,18 +10766,18 @@
         <v>16</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -11297,13 +11385,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD33">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="3">
+    <cfRule type="expression" dxfId="24" priority="3">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/excel_files/Ricks Music progress.xlsx
+++ b/docs/excel_files/Ricks Music progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\docs\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DC19FF-044D-4A4F-B65D-F6F7B30702FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77B0365-3392-475D-B349-FC08905D2D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23016" yWindow="12768" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
+    <workbookView xWindow="-23064" yWindow="12852" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="#" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="90">
   <si>
     <t>NA</t>
   </si>
@@ -307,6 +307,15 @@
   </si>
   <si>
     <t>Derek And The Dominos</t>
+  </si>
+  <si>
+    <t>current album</t>
+  </si>
+  <si>
+    <t>Arthur Lewis</t>
+  </si>
+  <si>
+    <t>Layla and …</t>
   </si>
 </sst>
 </file>
@@ -4337,7 +4346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5498BB1C-2009-4B75-8E63-FA8EC8D63D36}">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
@@ -4806,7 +4815,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>3</v>
@@ -4856,7 +4865,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>3</v>
@@ -4904,8 +4913,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:XFD11">
+  <conditionalFormatting sqref="A2:XFD12">
     <cfRule type="cellIs" dxfId="59" priority="7" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -4916,7 +4975,7 @@
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O11">
+  <conditionalFormatting sqref="O2:O12">
     <cfRule type="cellIs" dxfId="56" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -8407,82 +8466,84 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16921A6F-7CB8-4ECC-B4F3-AFD04063C385}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.28515625" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
@@ -8505,11 +8566,11 @@
         <v>3</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="L2" s="1" t="s">
         <v>3</v>
       </c>
@@ -8523,16 +8584,17 @@
         <v>3</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
@@ -8555,11 +8617,11 @@
         <v>3</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="L3" s="1" t="s">
         <v>3</v>
       </c>
@@ -8573,16 +8635,17 @@
         <v>3</v>
       </c>
       <c r="P3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
@@ -8605,11 +8668,11 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="L4" s="1" t="s">
         <v>3</v>
       </c>
@@ -8623,16 +8686,17 @@
         <v>3</v>
       </c>
       <c r="P4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -8655,11 +8719,11 @@
         <v>3</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="L5" s="1" t="s">
         <v>3</v>
       </c>
@@ -8673,16 +8737,17 @@
         <v>3</v>
       </c>
       <c r="P5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -8705,11 +8770,11 @@
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="L6" s="1" t="s">
         <v>3</v>
       </c>
@@ -8723,16 +8788,17 @@
         <v>3</v>
       </c>
       <c r="P6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
@@ -8752,13 +8818,13 @@
         <v>3</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>13</v>
@@ -8773,18 +8839,21 @@
         <v>13</v>
       </c>
       <c r="P7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>13</v>
@@ -8825,8 +8894,11 @@
       <c r="P8" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>82</v>
       </c>
@@ -8845,8 +8917,9 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q9" s="1"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -8863,8 +8936,9 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q10" s="1"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -8881,8 +8955,9 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -8899,8 +8974,9 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q12" s="1"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -8917,8 +8993,9 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q13" s="1"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -8935,8 +9012,9 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q14" s="1"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -8953,8 +9031,9 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q15" s="1"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -8971,8 +9050,9 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q16" s="1"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -8989,8 +9069,9 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q17" s="1"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -9007,8 +9088,9 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q18" s="1"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -9025,8 +9107,9 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -9043,8 +9126,9 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q20" s="1"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -9061,8 +9145,9 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q21" s="1"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -9079,8 +9164,9 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q22" s="1"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -9097,8 +9183,9 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q23" s="1"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -9115,8 +9202,9 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q24" s="1"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -9133,8 +9221,9 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q25" s="1"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -9151,8 +9240,9 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q26" s="1"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -9169,8 +9259,9 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q27" s="1"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -9187,8 +9278,9 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q28" s="1"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -9205,8 +9297,9 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q29" s="1"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -9223,8 +9316,9 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q30" s="1"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -9241,8 +9335,9 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q31" s="1"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -9259,8 +9354,9 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q32" s="1"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -9277,8 +9373,9 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q33" s="1"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -9295,6 +9392,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:XFD34">

--- a/docs/excel_files/Ricks Music progress.xlsx
+++ b/docs/excel_files/Ricks Music progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\docs\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77B0365-3392-475D-B349-FC08905D2D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA664B9-4590-424D-B822-C921EBDF1DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23064" yWindow="12852" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
+    <workbookView xWindow="23016" yWindow="12768" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="#" sheetId="4" r:id="rId1"/>
@@ -315,7 +315,7 @@
     <t>Arthur Lewis</t>
   </si>
   <si>
-    <t>Layla and …</t>
+    <t>No reason To Cry</t>
   </si>
 </sst>
 </file>

--- a/docs/excel_files/Ricks Music progress.xlsx
+++ b/docs/excel_files/Ricks Music progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\docs\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA664B9-4590-424D-B822-C921EBDF1DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A934227C-7D8C-4299-9221-B33DDD928869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23016" yWindow="12768" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="#" sheetId="4" r:id="rId1"/>
@@ -315,7 +315,7 @@
     <t>Arthur Lewis</t>
   </si>
   <si>
-    <t>No reason To Cry</t>
+    <t>Old Sock</t>
   </si>
 </sst>
 </file>
